--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Issue_register.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Issue_register.xlsx
@@ -12,17 +12,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
   <si>
     <t>Issue Register</t>
   </si>
   <si>
+    <t>OmniOps</t>
+  </si>
+  <si>
+    <t>CONFIDENTIAL</t>
+  </si>
+  <si>
     <t>Organisation</t>
   </si>
   <si>
-    <t>OmniOps</t>
-  </si>
-  <si>
     <t>Generated by</t>
   </si>
   <si>
@@ -32,7 +35,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-17 15:43 UTC</t>
+    <t>2026-09-23 10:59 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -41,6 +44,12 @@
     <t>SUBTREE</t>
   </si>
   <si>
+    <t>Document reference</t>
+  </si>
+  <si>
+    <t>1906-20260923105957</t>
+  </si>
+  <si>
     <t>Ref</t>
   </si>
   <si>
@@ -107,16 +116,16 @@
     <t>CAPAssigned</t>
   </si>
   <si>
-    <t>Hassan Rahman</t>
-  </si>
-  <si>
     <t>Mahmoud Abdulaziz</t>
   </si>
   <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
+    <t>Ibrahim Abdulaziz</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>47</t>
@@ -134,13 +143,13 @@
     <t>High</t>
   </si>
   <si>
-    <t>Salma Noor</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
+    <t>Rami Khalil</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>35</t>
@@ -167,16 +176,16 @@
     <t>RCSA-2026-01</t>
   </si>
   <si>
-    <t>Self-assessed ineffective control: AC-02</t>
+    <t>Self-assessed ineffective control: AC-04</t>
   </si>
   <si>
     <t>Open</t>
   </si>
   <si>
-    <t>2026-08-09</t>
-  </si>
-  <si>
-    <t>2026-10-08</t>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-11-14</t>
   </si>
   <si>
     <t>8</t>
@@ -186,7 +195,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -200,6 +209,16 @@
       <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF0F7A5A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF646F85"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="FF646F85"/>
       <sz val="9"/>
     </font>
@@ -210,7 +229,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0B1524"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -223,7 +242,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
+        <fgColor rgb="FF0F7A5A"/>
       </patternFill>
     </fill>
   </fills>
@@ -257,15 +276,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -613,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -625,36 +646,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -681,239 +720,239 @@
     <col min="13" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="D2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="I2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="J2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="K2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="L2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="M2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="N2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="F4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="7" t="s">
+      <c r="H5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>26</v>
+      <c r="J5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Issue_register.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Issue_register.xlsx
@@ -35,7 +35,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-23 10:59 UTC</t>
+    <t>2026-09-24 22:36 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -47,7 +47,7 @@
     <t>Document reference</t>
   </si>
   <si>
-    <t>1906-20260923105957</t>
+    <t>B7C7-20260924223634</t>
   </si>
   <si>
     <t>Ref</t>
@@ -116,16 +116,16 @@
     <t>CAPAssigned</t>
   </si>
   <si>
-    <t>Mahmoud Abdulaziz</t>
-  </si>
-  <si>
-    <t>Ibrahim Abdulaziz</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
+    <t>Shahd Hamdan</t>
+  </si>
+  <si>
+    <t>Alaa Tamimi</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
   </si>
   <si>
     <t>47</t>
@@ -143,13 +143,13 @@
     <t>High</t>
   </si>
   <si>
-    <t>Rami Khalil</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
+    <t>Saud Smadi</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
   </si>
   <si>
     <t>35</t>
@@ -176,16 +176,16 @@
     <t>RCSA-2026-01</t>
   </si>
   <si>
-    <t>Self-assessed ineffective control: AC-04</t>
+    <t>Self-assessed ineffective control: AC-02</t>
   </si>
   <si>
     <t>Open</t>
   </si>
   <si>
-    <t>2026-09-15</t>
-  </si>
-  <si>
-    <t>2026-11-14</t>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-11-15</t>
   </si>
   <si>
     <t>8</t>
@@ -934,7 +934,7 @@
         <v>55</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>29</v>
